--- a/etf_holdings/2026-09-29_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:08</t>
+          <t>2026-09-29 01:00:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:10</t>
+          <t>2026-09-29 01:01:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:11</t>
+          <t>2026-09-29 01:01:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:12</t>
+          <t>2026-09-29 01:01:03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-09-29_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:59</t>
+          <t>2026-09-29 01:39:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:01</t>
+          <t>2026-09-29 01:39:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:02</t>
+          <t>2026-09-29 01:39:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:03</t>
+          <t>2026-09-29 01:39:52</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-09-29_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.82%1,794,000</t>
+          <t>8.77%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.82%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.51%736,000</t>
+          <t>7.68%736,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>7.68%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.01%502</t>
+          <t>-1.79%493</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.58%5,709,000</t>
+          <t>5.66%5,709,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.66%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.31%753</t>
+          <t>-2.79%732</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.39%3,721,000</t>
+          <t>5.50%3,697,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3721000</v>
+        <v>3697000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,33 +753,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.39%180,000</t>
+          <t>4.37%179,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>4.37%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>180000</v>
+        <v>179000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.21%1,016,225</t>
+          <t>4.25%1,016,225</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.61%993</t>
+          <t>-6.45%929</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-6.45%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>993</v>
+        <v>929</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.96%2,041,000</t>
+          <t>4.00%2,041,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,33 +936,33 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2295</v>
+        <v>2185</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.75%820,000</t>
+          <t>3.69%815,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>820000</v>
+        <v>815000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.64%1555</t>
+          <t>-2.89%1510</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1555</v>
+        <v>1510</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.63%1,180,000</t>
+          <t>3.62%1,180,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.33%301,000</t>
+          <t>3.22%301,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5050</v>
+        <v>6020</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.07%311,000</t>
+          <t>3.10%251,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>311000</v>
+        <v>251000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6245</v>
+        <v>4920</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.07%252,000</t>
+          <t>3.08%309,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>252000</v>
+        <v>309000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.53%475.5</t>
+          <t>+4.84%498.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.84%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>475.5</v>
+        <v>498.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.94%3,158,000</t>
+          <t>2.97%3,158,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.54%372,000</t>
+          <t>2.61%372,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:48</t>
+          <t>2026-09-29 22:54:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-0.32%945</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1895</v>
+        <v>945</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.31%621,000</t>
+          <t>2.03%1,082,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>621000</v>
+        <v>1082000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.21%948</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>948</v>
+        <v>1810</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.04%1,089,000</t>
+          <t>2.02%541,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1089000</v>
+        <v>541000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,33 +1485,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.23%287</t>
+          <t>-2.09%281</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.80%3,230,000</t>
+          <t>1.82%3,216,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3230000</v>
+        <v>3216000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,20 +1546,20 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.36%554</t>
+          <t>-1.99%543</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.67%1,537,000</t>
+          <t>1.67%1,529,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1537000</v>
+        <v>1529000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,33 +1607,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.62%5,145,000</t>
+          <t>1.56%5,116,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>5145000</v>
+        <v>5116000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+3%722</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>722</v>
+        <v>19395</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.56%1,128,000</t>
+          <t>1.41%35,900</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1128000</v>
+        <v>35900</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>+1.11%730</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19835</v>
+        <v>730</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.43%35,900</t>
+          <t>1.37%964,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>35900</v>
+        <v>964000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,33 +1790,33 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.5%184.5</t>
+          <t>+0.54%185.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>184.5</v>
+        <v>185.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.30%3,660,000</t>
+          <t>1.33%3,638,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3660000</v>
+        <v>3638000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,20 +1851,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.26%190.5</t>
+          <t>-0.79%189</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>190.5</v>
+        <v>189</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.29%3,460,000</t>
+          <t>1.29%3,438,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3460000</v>
+        <v>3438000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.96%361.5</t>
+          <t>+0.27%189</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>361.5</v>
+        <v>189</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.26%1,749,000</t>
+          <t>1.27%3,415,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1749000</v>
+        <v>3415000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+2.17%188.5</t>
+          <t>+0.14%362</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>188.5</v>
+        <v>362</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.25%3,437,000</t>
+          <t>1.24%1,737,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3437000</v>
+        <v>1737000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>699</v>
+        <v>1485</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.24%906,000</t>
+          <t>1.23%418,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>906000</v>
+        <v>418000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,25 +2090,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1495</v>
+        <v>687</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.21%421,000</t>
+          <t>1.21%876,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>421000</v>
+        <v>876000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.25%94.5</t>
+          <t>-1.37%180.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>94.5</v>
+        <v>180.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.21%6,403,000</t>
+          <t>1.21%3,345,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>6403000</v>
+        <v>3345000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.67%183</t>
+          <t>+1.38%95.8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>183</v>
+        <v>95.8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.19%3,369,000</t>
+          <t>1.19%6,382,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3369000</v>
+        <v>6382000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:49</t>
+          <t>2026-09-29 22:55:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.65%1530</t>
+          <t>+3.59%1585</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1530</v>
+        <v>1585</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.16%382,000</t>
+          <t>1.15%382,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,20 +2339,20 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.2%255</t>
+          <t>-1.37%251.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>255</v>
+        <v>251.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.14%2,285,000</t>
+          <t>1.14%2,268,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>2285000</v>
+        <v>2268000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.17%287</t>
+          <t>+2.15%713</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>287</v>
+        <v>713</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.08%1,910,000</t>
+          <t>1.09%790,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1910000</v>
+        <v>790000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.01%698</t>
+          <t>-2.09%281</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>698</v>
+        <v>281</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.07%790,000</t>
+          <t>1.08%1,910,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>790000</v>
+        <v>1910000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%165</t>
+          <t>-2.42%161</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.07%3,302,000</t>
+          <t>1.07%3,280,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>3302000</v>
+        <v>3280000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.34%529</t>
+          <t>+2.84%544</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.34%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.03%1,000,000</t>
+          <t>1.04%1,000,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,20 +2644,20 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.42%120</t>
+          <t>-2.08%117.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>120</v>
+        <v>117.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.03%4,360,000</t>
+          <t>1.03%4,331,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>4360000</v>
+        <v>4331000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,20 +2705,20 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.33%151.5</t>
+          <t>-0.33%151</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>151.5</v>
+        <v>151</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.00%3,372,000</t>
+          <t>1.00%3,344,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3372000</v>
+        <v>3344000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.33%421.5</t>
+          <t>+0.24%422.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>421.5</v>
+        <v>422.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.89%1,032,000</t>
+          <t>0.86%1,032,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.01%902</t>
+          <t>0%902</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.80%455,000</t>
+          <t>0.81%455,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.86%234</t>
+          <t>+1.28%237</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.73%1,607,000</t>
+          <t>0.74%1,607,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.27%3230</t>
+          <t>+2.32%3305</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3230</v>
+        <v>3305</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.60%93,000</t>
+          <t>0.59%93,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+9.98%595</t>
+          <t>+4.2%620</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.40%380,000</t>
+          <t>0.45%380,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.91%565</t>
+          <t>-0.59%335.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>565</v>
+        <v>335.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.33%304,000</t>
+          <t>0.35%527,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>304000</v>
+        <v>527000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+9.93%337.5</t>
+          <t>-3.72%544</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>337.5</v>
+        <v>544</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.32%530,000</t>
+          <t>0.34%304,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>530000</v>
+        <v>304000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:50</t>
+          <t>2026-09-29 22:55:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.3%49.7</t>
+          <t>0%49.7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.31%3,212,000</t>
+          <t>0.32%3,212,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.41%122.5</t>
+          <t>+1.63%124.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+1.63%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>122.5</v>
+        <v>124.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.57%69.2</t>
+          <t>-0.72%68.7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>69.2</v>
+        <v>68.7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.21%242.5</t>
+          <t>-0.82%240.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>242.5</v>
+        <v>240.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.81%1010</t>
+          <t>+2.97%1040</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.81%</t>
+          <t>+2.97%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1010</v>
+        <v>1040</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.30%143,000</t>
+          <t>0.29%143,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.7%1155</t>
+          <t>+3.46%1195</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1155</v>
+        <v>1195</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-0.65%46.2</t>
+          <t>+0.11%46.25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>46.2</v>
+        <v>46.25</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0%171</t>
+          <t>-0.58%170</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3737,25 +3737,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1519華城</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-0.71%699</t>
+          <t>-2.54%498</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>699</v>
+        <v>498</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>&lt;0.01%660</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3798,25 +3798,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>1519華城</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+2.82%511</t>
+          <t>-1.57%688</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-1.57%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>511</v>
+        <v>688</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%660</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3825,11 +3825,11 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-0.8%49.6</t>
+          <t>-1.01%49.1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:52</t>
+          <t>2026-09-29 22:55:03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-1.96%150</t>
+          <t>+1%151.5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>150</v>
+        <v>151.5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-29_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:59</t>
+          <t>2026-09-29 23:50:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:00</t>
+          <t>2026-09-29 23:50:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:01</t>
+          <t>2026-09-29 23:50:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:03</t>
+          <t>2026-09-29 23:50:40</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
